--- a/4P_Index_Loi_2015-18_Code_Peche_Maritime.xlsx
+++ b/4P_Index_Loi_2015-18_Code_Peche_Maritime.xlsx
@@ -601,43 +601,39 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Maritime Fisheries Code adopted by the National Assembly on 30 June 2015 and promulgated on 13 July 2015 as Law No. 2015-18. Parliamentary legislation (Code), not executive implementing regulation (≠0.75).</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>maritime fisheries, artisanal fishing, industrial fishing, marine environment, maritime trade</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Art. 66: ban on gillnets made from nylon monofilament or multimonofilament elements; Art. 68: mandatory registration and marking of artisanal fishing vessels and gear; Art. 125: prohibited gear confiscated and destroyed.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Maritime Fisheries Code adopted by the National Assembly on 30 June 2015 and promulgated on 13 July 2015 as Law No. 2015-18. Parliamentary legislation (Code), not executive implementing regulation (≠0.75).</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>maritime fisheries, artisanal fishing, industrial fishing, marine environment, maritime trade</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>production, consumption, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>use, disposal, marine environment</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.25</v>
-      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Art. 64: fee for permits and authorisations (amount set by joint ministerial order); Arts. 123-127: criminal fines up to FCFA 30,000,000 for serious industrial fishing offences; no dedicated budget allocation for marine litter or gear recovery.</t>
+          <t>Art. 64: fee for permits and authorisations (amount set by joint ministerial order); Arts. 123-127: criminal fines up to FCFA 30,000,000 for serious industrial fishing offences.</t>
         </is>
       </c>
       <c r="O2" s="3">
@@ -649,7 +645,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -698,43 +694,39 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Maritime Fisheries Code adopted by the National Assembly on 30 June 2015 and promulgated on 13 July 2015 as Law No. 2015-18. Parliamentary legislation (Code), not executive implementing regulation (≠0.75).</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>maritime fisheries, artisanal fishing, industrial fishing, marine environment, maritime trade</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Art. 66: ban on gillnets made from nylon monofilament or multimonofilament elements; Art. 68: mandatory registration and marking of artisanal fishing vessels and gear; Art. 125: prohibited gear confiscated and destroyed.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Maritime Fisheries Code adopted by the National Assembly on 30 June 2015 and promulgated on 13 July 2015 as Law No. 2015-18. Parliamentary legislation (Code), not executive implementing regulation (≠0.75).</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>maritime fisheries, artisanal fishing, industrial fishing, marine environment, maritime trade</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>production, consumption, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>use, disposal, marine environment</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.25</v>
-      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Art. 64: fee for permits and authorisations (amount set by joint ministerial order); Arts. 123-127: criminal fines up to FCFA 30,000,000 for serious industrial fishing offences; no dedicated budget allocation for marine litter or gear recovery.</t>
+          <t>Art. 64: fee for permits and authorisations (amount set by joint ministerial order); Arts. 123-127: criminal fines up to FCFA 30,000,000 for serious industrial fishing offences.</t>
         </is>
       </c>
       <c r="O3" s="3">
@@ -742,11 +734,11 @@
         <v/>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -771,7 +763,7 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Gear traceability and marking — relevant for identifying and recovering abandoned gear.</t>
+          <t>Mandatory gear registration and marking — regulatory traceability for identifying and recovering abandoned gear.</t>
         </is>
       </c>
     </row>
@@ -795,43 +787,39 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Maritime Fisheries Code adopted by the National Assembly on 30 June 2015 and promulgated on 13 July 2015 as Law No. 2015-18. Parliamentary legislation (Code), not executive implementing regulation (≠0.75).</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>maritime fisheries, artisanal fishing, industrial fishing, marine environment, maritime trade</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Art. 66: ban on gillnets made from nylon monofilament or multimonofilament elements; Art. 68: mandatory registration and marking of artisanal fishing vessels and gear; Art. 125: prohibited gear confiscated and destroyed.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Maritime Fisheries Code adopted by the National Assembly on 30 June 2015 and promulgated on 13 July 2015 as Law No. 2015-18. Parliamentary legislation (Code), not executive implementing regulation (≠0.75).</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>maritime fisheries, artisanal fishing, industrial fishing, marine environment, maritime trade</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>production, consumption, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>use, disposal, marine environment</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.25</v>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Art. 64: fee for permits and authorisations (amount set by joint ministerial order); Arts. 123-127: criminal fines up to FCFA 30,000,000 for serious industrial fishing offences; no dedicated budget allocation for marine litter or gear recovery.</t>
+          <t>Art. 64: fee for permits and authorisations (amount set by joint ministerial order); Arts. 123-127: criminal fines up to FCFA 30,000,000 for serious industrial fishing offences.</t>
         </is>
       </c>
       <c r="O4" s="3">
@@ -843,7 +831,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Disposal</t>
+          <t>End of life</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
